--- a/artfynd/A 22918-2026 artfynd.xlsx
+++ b/artfynd/A 22918-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>75330909</v>
       </c>
       <c r="B2" t="n">
-        <v>78473</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582081.0032692659</v>
+        <v>582081</v>
       </c>
       <c r="R2" t="n">
-        <v>7095782.012067153</v>
+        <v>7095782</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75330910</v>
+        <v>75330908</v>
       </c>
       <c r="B3" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>715</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582107.1609945181</v>
+        <v>581999</v>
       </c>
       <c r="R3" t="n">
-        <v>7095841.130739488</v>
+        <v>7095715</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,21 +857,11 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -907,11 +877,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # klen asplåga</t>
+          <t>2 substratenheter # äldre asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75330908</v>
+        <v>75330911</v>
       </c>
       <c r="B4" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581999.1879342541</v>
+        <v>582140</v>
       </c>
       <c r="R4" t="n">
-        <v>7095714.839109732</v>
+        <v>7095900</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,21 +971,11 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1036,11 +991,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # äldre asp</t>
+          <t>1 substratenheter # äldre asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,37 +1017,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75330911</v>
+        <v>75330910</v>
       </c>
       <c r="B5" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>388</v>
+        <v>715</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582139.9229406307</v>
+        <v>582107</v>
       </c>
       <c r="R5" t="n">
-        <v>7095899.983145155</v>
+        <v>7095841</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,19 +1085,9 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-07-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1109,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre asp</t>
+          <t>1 substratenheter # klen asplåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1194,12 +1134,7 @@
         <v>75330912</v>
       </c>
       <c r="B6" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582187.0500814903</v>
+        <v>582187</v>
       </c>
       <c r="R6" t="n">
-        <v>7095830.933349297</v>
+        <v>7095831</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1264,19 +1199,9 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-07-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1313,6 +1238,120 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>75330907</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92732</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kortingvattnet, V om, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>581974</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7095509</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-07-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-07-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>90-årig fin lövbränna</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # klen asplåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
